--- a/data/27April-Razorbacks-v-89ers.xlsx
+++ b/data/27April-Razorbacks-v-89ers.xlsx
@@ -232,7 +232,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O109"/>
   <sheetData>
     <row r="1">
@@ -353,8 +353,10 @@
       <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
-        <v>22</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>DCUCRM</t>
+        </is>
       </c>
       <c r="J7" t="s">
         <v>18</v>
@@ -607,8 +609,10 @@
       <c r="D32" t="s">
         <v>16</v>
       </c>
-      <c r="E32" t="s">
-        <v>33</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LCDN</t>
+        </is>
       </c>
       <c r="J32" t="s">
         <v>18</v>
@@ -804,8 +808,10 @@
       <c r="D51" t="s">
         <v>16</v>
       </c>
-      <c r="E51" t="s">
-        <v>43</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>DCUMLM</t>
+        </is>
       </c>
       <c r="J51" t="s">
         <v>18</v>
@@ -1156,8 +1162,10 @@
       <c r="D83" t="s">
         <v>16</v>
       </c>
-      <c r="E83" t="s">
-        <v>61</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I83" t="s">
         <v>62</v>
@@ -1277,8 +1285,10 @@
       <c r="D94" t="s">
         <v>16</v>
       </c>
-      <c r="E94" t="s">
-        <v>61</v>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>DC</t>
+        </is>
       </c>
       <c r="I94" t="s">
         <v>64</v>
